--- a/human_validation/judge/kor/judge_D010_S003_P001__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D010_S003_P001__llama-3.3-70b-instruct_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B83"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,418 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 진료실에 오신 것을 환영합니다. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 식사가 진짜 엉망이 돼서 왔어요. 식단 기록하는 것도 신경을 안 쓰게 됐고, 며칠씩 제대로 된 끼니를 거르고 있어요—거의 커피랑 단백질바만 먹고요. 그러다 옷이 헐렁해지는 걸 알아챘어요, 몸에서 그냥 흘러내리는 것처럼요, 근데 그게 언제부터 그랬는지도 몰랐어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 체중이 느는 것이 두려우신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 아닌 것 같아요. 그러니까, 살을 빼려고 하는 것도 아니고 찌는 걸 피하려는 것도 아니에요. 그냥 정상적으로 먹지를 못하고 있었던 거고, 옷이 헐렁해지기 전까지는 체중이 빠지는 것도 제대로 알아채지 못했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 체중이 늘까 봐 걱정했던 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 딱히 기억이 안 나요. 체중 느는 걸 특별히 걱정했던 시기가 있었던 것 같지 않아요. 그냥 제가 그다지 신경 써본 부분이 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 짧은 시간 안에 많은 양의 음식을 먹으면서 멈출 수 없다고 느낀 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 잘 모르겠어요. 그런 식으로 확실하게 겪은 적이 있었던 것 같지 않아요—많은 양을 먹고 멈추지 못하는 느낌이요. 딱히 떠오르는 게 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 최근에 체중이 상당히 많이 빠지셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네, 그런 것 같아요. 체중을 자주 재진 않았는데, 식사가 정말 엉망이 됐거든요. 식단 기록도 안 하고, 며칠씩 제대로 된 끼니를 거르고, 거의 커피랑 단백질바만 먹었어요. 그러다 체중이 빠졌다는 걸 제대로 알아채기 전에 옷이 헐렁해지기 시작했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 인생에서 체중이 느는 것에 대해 두려움을 느낀 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 아니요, 없는 것 같아요. 체중이 느는 게 진짜로 두려웠던 때가 기억나지 않아요. 그게 저한테 실제로 문제였던 적은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 음식에 대한 흥미가 없다고 느끼시나요, 아니면 그냥 먹는 것 자체를 생각하지 않게 되는 건가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 그냥 먹는 걸 생각하지 않게 되는 쪽에 가까워요. 식단 기록에 신경을 안 쓰게 됐고, 그러다 며칠씩 제대로 된 음식을 안 먹게 됐어요—그냥 커피랑 단백질바만요. 옷이 헐렁해지기 전까지는 상황이 얼마나 나빠졌는지도 제대로 몰랐어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 정상적인 식사를 생각할 때 불안하거나 속상한 느낌이 드시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 딱히 불안하거나 속상하지는 않아요. 정상적인 식사가 무섭거나 그런 건 아니에요. 그냥... 음식에 대해 별로 생각을 안 하게 됐고, 식사가 그냥 제 관심 밖으로 밀려난 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 생리 주기에 변화가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 저는 남자라서 생리 주기가 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 식습관이 변한 게 체형에 대한 걱정 때문이라고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 아니요, 체형 때문은 아닌 것 같아요. 살을 빼려고 하거나 외모를 바꾸려고 했던 게 아니에요. 그냥 먹는 것 자체에 별로 신경을 못 썼어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 체중이 늘까 봐 음식을 피하시는 경우가 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 아니요, 체중이 늘까 봐 음식을 피한 건 아니었어요. 그보다는 그냥 제대로 먹는 것에 신경을 안 쓰게 된 거였어요. 며칠씩 제대로 된 끼니를 거르고 커피나 단백질바로 때웠고, 그러다 제대로 알아채기도 전에 옷이 헐렁해지기 시작했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 체중 감소가 의도치 않은 것이었다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 네, 의도한 게 아니었어요. 살을 빼려고 한 게 아니었거든요. 그냥 식사가 완전히 궤도를 벗어났어요—식단 기록도 안 하고, 며칠씩 제대로 된 끼니를 거르고, 거의 커피나 단백질바로만 버텼고, 그러다 옷이 헐렁해진 걸 알아챘어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 식습관이 변한 게 겪고 계신 감정적인 문제나 스트레스 때문이라고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 네, 아마 스트레스나 감정적으로 뭔가 있었던 게 영향을 준 것 같아요. 그냥 식단 기록이나 식사 준비에 신경을 안 쓰게 됐어요. 며칠씩 제대로 된 끼니 없이 지냈고, 커피랑 단백질바만 먹었고, 그러다 제대로 알아채기도 전에 옷이 헐렁해져 있었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 식습관 변화를 유발했다고 생각되는 특정한 스트레스 사건이나 시기가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 네. 직장에서 임시로 PMO급 책임을 맡게 된 후부터였어요. 갑자기 그런 건 아니고, 한 3주 정도에 걸쳐 여러 가지가 쌓이면서 그때부터 식사가 흐트러지기 시작했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 적응장애 (D020) | 지속성 우울장애 (D014) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 한번 먹기 시작하면 멈추지 못할 것 같다고 느끼신 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 딱히 없어요. 오히려 반대였던 것 같아요—식사가 궤도를 벗어나면서 며칠씩 제대로 된 끼니를 거르고 커피나 단백질바로 버텼어요. 일부러 그런 게 아니라 그냥 신경을 못 쓰게 된 거고, 그러다 제대로 알아채기도 전에 옷이 헐렁해지기 시작했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 적응장애 (D020) | 지속성 우울장애 (D014) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 정상적인 양을 먹기 시작하면 먹는 양을 조절하지 못할까 봐 걱정되시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 아니요, 과식하거나 시작하면 통제력을 잃을까 봐 걱정하지는 않아요. 오히려 제 식사는 반대 방향으로 완전히 궤도를 벗어났어요—뭐든 기록하는 데 신경을 안 쓰게 됐고, 며칠씩 제대로 된 끼니를 거르고, 커피랑 단백질바로만 버텼어요. 제대로 알아채기도 전에 옷이 헐렁해지기 시작했고요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 적응장애 (D020) | 지속성 우울장애 (D014) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 다시 정상적으로 먹기 시작하면 먹는 양에 대한 통제력을 잃을 것 같다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 아니요, 정상적으로 먹으면 통제력을 잃을 것 같다는 느낌은 별로 없어요. 문제는 오히려 그냥 음식에 아예 신경을 안 쓰게 됐다는 거예요—기록을 그만뒀고, 며칠씩 제대로 된 끼니를 거르고, 기본적으로 커피랑 단백질바로 버텼어요. 제대로 알아채기도 전에 옷이 헐렁해지기 시작했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 적응장애 (D020) | 지속성 우울장애 (D014) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 인생에서 체중이 느는 것에 두려움을 느낀 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 없는 것 같아요. 그러니까, 대부분의 사람들처럼 외모에 신경을 쓰긴 하지만, 체중이 느는 게 두려웠던 기억은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 적응장애 (D020) | 지속성 우울장애 (D014) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사 질문] 잃었던 체중을 다시 회복한다면 식습관이 달라질 것 같다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 환자 응답] 체중을 다시 회복한다고 해서 문제가 크게 달라질 것 같지는 않아요. 체중 때문에 일부러 덜 먹었던 게 아니었거든요. 그냥 식단 기록에 신경을 안 쓰게 됐고, 며칠씩 제대로 된 끼니를 거르고, 거의 커피랑 단백질바로 버텼어요. 체중 감소는 옷이 헐렁해지기 시작하고 나서야 알아챈, 그냥 그 결과였던 거예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사의 감별진단] 적응장애 (D020) | 지속성 우울장애 (D014) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>진단명: 정신병적 양상을 동반한 제1형 양극성장애 (D010)
 인구통계: 성별 남성 / 나이 30 / 직업상태 project management specialist / 최종학력 학사
@@ -575,485 +978,46 @@
 증상 지속 기간: None
 추가 요건: delusions_and_hallucinations occur exclusively during the manic episode
 주호소 증상 코드: S026
-배경 서술: 정씨는 고예산 기술 도입 프로젝트에서 임시로 PMO급 책임을 맡게 되자, 이를 자기 경력의 결정적인 시험대로 받아들이고 평소 쓰던 스프레드시트와 대시보드, 최적화 루틴을 하루 종일 확장해 쓰기 시작했다. 이후 3주에 걸쳐 원래도 경쟁적이었던 그의 업무 스타일은 눈에 띄게 고조되고 예민한 강도로 치달았고, 수면 시간이 줄고, 계획이 빠르게 앞서 나가고, 압박감 있는 발표를 하며, 자신만이 회사의 전체 운영 모델을 재설계할 수 있다는 거창한 확신을 보였다. 뒤이어 생생한 환각 경험이 나타났고, 급격한 우울 삽화로 떨어지면서 등산, 사진, 식단 기록, 목공에 대한 흥미를 잃었다. 그가 중요한 프로젝트 인수인계를 놓치고, 밤늦게 정리되지 않은 전략 문서를 보내며, 프로젝트 후원자가 그의 판단력에 의문을 제기한 뒤 죽음에 대한 생각을 표현하면서 기능 저하가 뚜렷해졌다. 회사 보안팀과 상사가 혼란스러웠던 전체 회의와 그 후 이어진 자살 관련 발언 때문에 그를 응급실로 데려가면서 그는 정신과 진료를 받게 되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 진료실에 오신 것을 환영합니다. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 식사가 진짜 엉망이 돼서 왔어요. 식단 기록하는 것도 신경을 안 쓰게 됐고, 며칠씩 제대로 된 끼니를 거르고 있어요—거의 커피랑 단백질바만 먹고요. 그러다 옷이 헐렁해지는 걸 알아챘어요, 몸에서 그냥 흘러내리는 것처럼요, 근데 그게 언제부터 그랬는지도 몰랐어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 체중이 느는 것이 두려우신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 아닌 것 같아요. 그러니까, 살을 빼려고 하는 것도 아니고 찌는 걸 피하려는 것도 아니에요. 그냥 정상적으로 먹지를 못하고 있었던 거고, 옷이 헐렁해지기 전까지는 체중이 빠지는 것도 제대로 알아채지 못했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 체중이 늘까 봐 걱정했던 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 딱히 기억이 안 나요. 체중 느는 걸 특별히 걱정했던 시기가 있었던 것 같지 않아요. 그냥 제가 그다지 신경 써본 부분이 아니에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 짧은 시간 안에 많은 양의 음식을 먹으면서 멈출 수 없다고 느낀 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 잘 모르겠어요. 그런 식으로 확실하게 겪은 적이 있었던 것 같지 않아요—많은 양을 먹고 멈추지 못하는 느낌이요. 딱히 떠오르는 게 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 최근에 체중이 상당히 많이 빠지셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네, 그런 것 같아요. 체중을 자주 재진 않았는데, 식사가 정말 엉망이 됐거든요. 식단 기록도 안 하고, 며칠씩 제대로 된 끼니를 거르고, 거의 커피랑 단백질바만 먹었어요. 그러다 체중이 빠졌다는 걸 제대로 알아채기 전에 옷이 헐렁해지기 시작했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 인생에서 체중이 느는 것에 대해 두려움을 느낀 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 아니요, 없는 것 같아요. 체중이 느는 게 진짜로 두려웠던 때가 기억나지 않아요. 그게 저한테 실제로 문제였던 적은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 음식에 대한 흥미가 없다고 느끼시나요, 아니면 그냥 먹는 것 자체를 생각하지 않게 되는 건가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 그냥 먹는 걸 생각하지 않게 되는 쪽에 가까워요. 식단 기록에 신경을 안 쓰게 됐고, 그러다 며칠씩 제대로 된 음식을 안 먹게 됐어요—그냥 커피랑 단백질바만요. 옷이 헐렁해지기 전까지는 상황이 얼마나 나빠졌는지도 제대로 몰랐어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 지속성 우울장애 (D014) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 정상적인 식사를 생각할 때 불안하거나 속상한 느낌이 드시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 딱히 불안하거나 속상하지는 않아요. 정상적인 식사가 무섭거나 그런 건 아니에요. 그냥... 음식에 대해 별로 생각을 안 하게 됐고, 식사가 그냥 제 관심 밖으로 밀려난 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 지속성 우울장애 (D014) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 생리 주기에 변화가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 저는 남자라서 생리 주기가 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 중간확률: 지속성 우울장애 (D014) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 식습관이 변한 게 체형에 대한 걱정 때문이라고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 아니요, 체형 때문은 아닌 것 같아요. 살을 빼려고 하거나 외모를 바꾸려고 했던 게 아니에요. 그냥 먹는 것 자체에 별로 신경을 못 썼어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 중간확률: 지속성 우울장애 (D014) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 체중이 늘까 봐 음식을 피하시는 경우가 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 아니요, 체중이 늘까 봐 음식을 피한 건 아니었어요. 그보다는 그냥 제대로 먹는 것에 신경을 안 쓰게 된 거였어요. 며칠씩 제대로 된 끼니를 거르고 커피나 단백질바로 때웠고, 그러다 제대로 알아채기도 전에 옷이 헐렁해지기 시작했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 중간확률: 지속성 우울장애 (D014) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 체중 감소가 의도치 않은 것이었다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 네, 의도한 게 아니었어요. 살을 빼려고 한 게 아니었거든요. 그냥 식사가 완전히 궤도를 벗어났어요—식단 기록도 안 하고, 며칠씩 제대로 된 끼니를 거르고, 거의 커피나 단백질바로만 버텼고, 그러다 옷이 헐렁해진 걸 알아챘어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 중간확률: 지속성 우울장애 (D014) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 식습관이 변한 게 겪고 계신 감정적인 문제나 스트레스 때문이라고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 네, 아마 스트레스나 감정적으로 뭔가 있었던 게 영향을 준 것 같아요. 그냥 식단 기록이나 식사 준비에 신경을 안 쓰게 됐어요. 며칠씩 제대로 된 끼니 없이 지냈고, 커피랑 단백질바만 먹었고, 그러다 제대로 알아채기도 전에 옷이 헐렁해져 있었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 중간확률: 지속성 우울장애 (D014) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 식습관 변화를 유발했다고 생각되는 특정한 스트레스 사건이나 시기가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 네. 직장에서 임시로 PMO급 책임을 맡게 된 후부터였어요. 갑자기 그런 건 아니고, 한 3주 정도에 걸쳐 여러 가지가 쌓이면서 그때부터 식사가 흐트러지기 시작했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 지속성 우울장애 (D014) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 한번 먹기 시작하면 멈추지 못할 것 같다고 느끼신 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 딱히 없어요. 오히려 반대였던 것 같아요—식사가 궤도를 벗어나면서 며칠씩 제대로 된 끼니를 거르고 커피나 단백질바로 버텼어요. 일부러 그런 게 아니라 그냥 신경을 못 쓰게 된 거고, 그러다 제대로 알아채기도 전에 옷이 헐렁해지기 시작했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 지속성 우울장애 (D014) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 정상적인 양을 먹기 시작하면 먹는 양을 조절하지 못할까 봐 걱정되시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 아니요, 과식하거나 시작하면 통제력을 잃을까 봐 걱정하지는 않아요. 오히려 제 식사는 반대 방향으로 완전히 궤도를 벗어났어요—뭐든 기록하는 데 신경을 안 쓰게 됐고, 며칠씩 제대로 된 끼니를 거르고, 커피랑 단백질바로만 버텼어요. 제대로 알아채기도 전에 옷이 헐렁해지기 시작했고요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 지속성 우울장애 (D014) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 다시 정상적으로 먹기 시작하면 먹는 양에 대한 통제력을 잃을 것 같다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 아니요, 정상적으로 먹으면 통제력을 잃을 것 같다는 느낌은 별로 없어요. 문제는 오히려 그냥 음식에 아예 신경을 안 쓰게 됐다는 거예요—기록을 그만뒀고, 며칠씩 제대로 된 끼니를 거르고, 기본적으로 커피랑 단백질바로 버텼어요. 제대로 알아채기도 전에 옷이 헐렁해지기 시작했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 지속성 우울장애 (D014) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 인생에서 체중이 느는 것에 두려움을 느낀 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 없는 것 같아요. 그러니까, 대부분의 사람들처럼 외모에 신경을 쓰긴 하지만, 체중이 느는 게 두려웠던 기억은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 지속성 우울장애 (D014) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사 질문] 잃었던 체중을 다시 회복한다면 식습관이 달라질 것 같다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 환자 응답] 체중을 다시 회복한다고 해서 문제가 크게 달라질 것 같지는 않아요. 체중 때문에 일부러 덜 먹었던 게 아니었거든요. 그냥 식단 기록에 신경을 안 쓰게 됐고, 며칠씩 제대로 된 끼니를 거르고, 거의 커피랑 단백질바로 버텼어요. 체중 감소는 옷이 헐렁해지기 시작하고 나서야 알아챈, 그냥 그 결과였던 거예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
+배경 서술: 정씨는 고예산 기술 도입 프로젝트에서 임시로 PMO급 책임을 맡게 되자, 이를 자기 경력의 결정적인 시험대로 받아들이고 평소 쓰던 스프레드시트와 대시보드, 최적화 루틴을 하루 종일 확장해 쓰기 시작했다. 이후 3주에 걸쳐 원래도 경쟁적이었던 그의 업무 스타일은 눈에 띄게 고조되고 예민한 강도로 치달았고, 수면 시간이 줄고, 계획이 빠르게 앞서 나가고, 압박감 있는 발표를 하며, 자신만이 회사의 전체 운영 모델을 재설계할 수 있다는 거창한 확신을 보였다. 뒤이어 생생한 환각 경험이 나타났고, 급격한 우울 삽화로 떨어지면서 등산, 사진, 식단 기록, 목공에 대한 흥미를 잃었다. 그가 중요한 프로젝트 인수인계를 놓치고, 밤늦게 정리되지 않은 전략 문서를 보내며, 프로젝트 후원자가 그의 판단력에 의문을 제기한 뒤 죽음에 대한 생각을 표현하면서 기능 저하가 뚜렷해졌다. 회사 보안팀과 상사가 혼란스러웠던 전체 회의와 그 후 이어진 자살 관련 발언 때문에 그를 응급실로 데려가면서 그는 정신과 진료를 받게 되었다.
+표집된 증상 목록:
+  - S020 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
+  - S024 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - S025 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - S026 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S032 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.
+  - S033 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.
+  - S034 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.
+  - S035 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).
+  - S036 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).
+  - S037 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.
+  - S038 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.</t>
+        </is>
+      </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>[19번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 지속성 우울장애 (D014) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 신경성 식욕부진증 (D021, ICD: F50.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: manic_episode (관계=must_include, 요구개수=5, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.; 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.; 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).; 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).; 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.; 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.; 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.; 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.; 위험 결과 초래 행동: 고통스러운 결과를 초래할 가능성이 높은 활동에 지나치게 몰두함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=include, 요구개수=5, 충족개수=1, 커버리지=0.2)
-  확인된 근거: 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
-  누락: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.; 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.</t>
+          <t>의사의 최종 진단: 신경성 식욕부진증 (D021, ICD: F50.0)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: 없음
+체크리스트 그룹: manic_episode (관계=must_include, 요구개수=5, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)
+체크리스트 그룹: depressive_episode (관계=include, 요구개수=5, 충족개수=1, 커버리지=0.2)
+확인된 근거:
+  - 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A73:B73"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D010_S003_P001__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D010_S003_P001__llama-3.3-70b-instruct_kor.xlsx
@@ -964,6 +964,11 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -1013,11 +1018,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A73:B73"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D010_S003_P001__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D010_S003_P001__llama-3.3-70b-instruct_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.3056</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
